--- a/payrollsystem/docs/test cases/test_log.xlsx
+++ b/payrollsystem/docs/test cases/test_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06d0fef4c6ce3e76/Desktop/Summer2025/SDEV268/M8/payrollsystem/docs/test cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="8_{626B5BD4-8053-4E84-BFC4-F018141E1163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0D31033-662B-42C7-9772-077D90582B23}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{626B5BD4-8053-4E84-BFC4-F018141E1163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF1C46BE-E975-4F05-B3DF-E25FA2F3EE6B}"/>
   <bookViews>
     <workbookView xWindow="53370" yWindow="1755" windowWidth="48900" windowHeight="15345" xr2:uid="{325F4D7B-BDF1-45C8-AC64-0C2DE388B1F2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="226">
   <si>
     <t>ID</t>
   </si>
@@ -710,6 +710,9 @@
   </si>
   <si>
     <t>History of Employee Payroll</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/tc-001.png</t>
   </si>
 </sst>
 </file>
@@ -1644,6 +1647,9 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
+      <c r="H2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="str">

--- a/payrollsystem/docs/test cases/test_log.xlsx
+++ b/payrollsystem/docs/test cases/test_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06d0fef4c6ce3e76/Desktop/Summer2025/SDEV268/M8/payrollsystem/docs/test cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{626B5BD4-8053-4E84-BFC4-F018141E1163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF1C46BE-E975-4F05-B3DF-E25FA2F3EE6B}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{626B5BD4-8053-4E84-BFC4-F018141E1163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5E1C66D-08EC-4F56-9B59-718ECBEB7AE8}"/>
   <bookViews>
-    <workbookView xWindow="53370" yWindow="1755" windowWidth="48900" windowHeight="15345" xr2:uid="{325F4D7B-BDF1-45C8-AC64-0C2DE388B1F2}"/>
+    <workbookView xWindow="2640" yWindow="3330" windowWidth="48900" windowHeight="15345" xr2:uid="{325F4D7B-BDF1-45C8-AC64-0C2DE388B1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="test_log" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="251">
   <si>
     <t>ID</t>
   </si>
@@ -148,24 +148,12 @@
     <t>Gender restricted values</t>
   </si>
   <si>
-    <t>Invalid gender value</t>
-  </si>
-  <si>
-    <t>Choose invalid value or type</t>
-  </si>
-  <si>
     <t>Validation error</t>
   </si>
   <si>
     <t>Pay type only Salary or Hourly</t>
   </si>
   <si>
-    <t>Invalid pay type</t>
-  </si>
-  <si>
-    <t>Enter other value</t>
-  </si>
-  <si>
     <t>Invalid values</t>
   </si>
   <si>
@@ -292,9 +280,6 @@
     <t>Date Format</t>
   </si>
   <si>
-    <t>Invalid Date</t>
-  </si>
-  <si>
     <t>Enter an incorrect date format</t>
   </si>
   <si>
@@ -697,9 +682,6 @@
     <t>Database Creation</t>
   </si>
   <si>
-    <t>databases correctly initialized</t>
-  </si>
-  <si>
     <t>Employee Payroll History</t>
   </si>
   <si>
@@ -713,6 +695,99 @@
   </si>
   <si>
     <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/tc-001.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-002.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-003</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-004</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-005.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-006.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-007.png</t>
+  </si>
+  <si>
+    <t>Binary Option</t>
+  </si>
+  <si>
+    <t>Choose Gender</t>
+  </si>
+  <si>
+    <t>Gender selected</t>
+  </si>
+  <si>
+    <t>Binary option</t>
+  </si>
+  <si>
+    <t>Choose hourly or salary</t>
+  </si>
+  <si>
+    <t>pay type selected</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-008.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-009.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-010.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-011</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-012.png</t>
+  </si>
+  <si>
+    <t>All Databases updated correctly</t>
+  </si>
+  <si>
+    <t>databases exist</t>
+  </si>
+  <si>
+    <t>all time entries, employee information, etc</t>
+  </si>
+  <si>
+    <t>All time entries, and Employee demographics added</t>
+  </si>
+  <si>
+    <t>databases correctly initialized and updated with employee information</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-013</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-014.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-015.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-016.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/blob/main/payrollsystem/docs/test%20cases/screenshots/TC-017.png</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-018</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-019</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-020</t>
+  </si>
+  <si>
+    <t>https://github.com/rgwin1/sdev268fp/tree/main/payrollsystem/docs/test%20cases/screenshots/TC-021</t>
   </si>
 </sst>
 </file>
@@ -1597,8 +1672,8 @@
     <col min="4" max="4" width="44.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="98.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1648,7 +1723,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1674,6 +1749,9 @@
       <c r="G3" t="s">
         <v>17</v>
       </c>
+      <c r="H3" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
@@ -1690,13 +1768,16 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1722,6 +1803,9 @@
       <c r="G5" t="s">
         <v>26</v>
       </c>
+      <c r="H5" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
@@ -1732,19 +1816,22 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1767,6 +1854,9 @@
       <c r="G7" t="s">
         <v>31</v>
       </c>
+      <c r="H7" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
@@ -1788,6 +1878,9 @@
       <c r="G8" t="s">
         <v>35</v>
       </c>
+      <c r="H8" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
@@ -1801,13 +1894,16 @@
         <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>228</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1819,16 +1915,19 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>229</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>231</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1840,16 +1939,19 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1861,16 +1963,19 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1879,43 +1984,49 @@
         <v>TC-012</v>
       </c>
       <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
         <v>73</v>
       </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" t="s">
-        <v>77</v>
+      <c r="H13" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
-        <f t="shared" si="0"/>
+        <f>"TC-" &amp; TEXT(ROW()-1,"000")</f>
         <v>TC-013</v>
       </c>
       <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
         <v>78</v>
       </c>
-      <c r="C14" t="s">
+      <c r="G14" t="s">
         <v>79</v>
       </c>
-      <c r="D14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" t="s">
-        <v>83</v>
+      <c r="H14" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1924,22 +2035,25 @@
         <v>TC-014</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1948,187 +2062,231 @@
         <v>TC-015</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F16" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G16" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>TC-016</v>
       </c>
       <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
         <v>44</v>
       </c>
-      <c r="C17" t="s">
+      <c r="G17" t="s">
         <v>45</v>
       </c>
-      <c r="D17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>TC-017</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" t="s">
         <v>50</v>
       </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>TC-018</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E19" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F19" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G19" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <f t="shared" si="0"/>
+        <f>"TC-" &amp; TEXT(ROW()-1,"000")</f>
         <v>TC-019</v>
       </c>
       <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" t="s">
         <v>55</v>
       </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>TC-020</v>
       </c>
       <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
         <v>60</v>
       </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>TC-021</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>TC-022</v>
       </c>
       <c r="B23" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" t="s">
+        <v>239</v>
+      </c>
+      <c r="F23" t="s">
+        <v>240</v>
       </c>
       <c r="G23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>TC-023</v>
       </c>
       <c r="B24" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D24" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F24" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G24" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{7B55DF5C-68F8-42E3-BD73-0DADB0949329}"/>
+    <hyperlink ref="H9" r:id="rId2" xr:uid="{9E5E37BB-0729-4D69-9FA7-DC8863F9D5B6}"/>
+    <hyperlink ref="H10" r:id="rId3" xr:uid="{A16881D4-0172-446D-B6C4-64C1F9BBBC1D}"/>
+    <hyperlink ref="H12" r:id="rId4" xr:uid="{07E2E02F-0016-4476-ACBF-915F543F82B4}"/>
+    <hyperlink ref="H16" r:id="rId5" xr:uid="{CCB10881-E1CD-4818-8DDC-29D59ED1F714}"/>
+    <hyperlink ref="H19" r:id="rId6" xr:uid="{C18489D9-B2BF-4FB6-932B-07DA16495217}"/>
+    <hyperlink ref="H20" r:id="rId7" xr:uid="{27B14051-1501-4D24-BAF0-4B7CB26011B1}"/>
+    <hyperlink ref="H21" r:id="rId8" xr:uid="{55DA3C32-E788-467B-9219-7B98002A838B}"/>
+    <hyperlink ref="H22" r:id="rId9" xr:uid="{DAD3F5A8-2FFF-4B1B-9339-C16A1A274D89}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2151,43 +2309,43 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1">
         <v>31120</v>
       </c>
       <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" t="s">
         <v>98</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
         <v>99</v>
       </c>
-      <c r="H1" t="s">
+      <c r="N1" t="s">
         <v>100</v>
-      </c>
-      <c r="I1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N1" t="s">
-        <v>105</v>
       </c>
       <c r="O1">
         <v>46201</v>
@@ -2195,43 +2353,43 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1">
         <v>33076</v>
       </c>
       <c r="F2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" t="s">
         <v>109</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
         <v>110</v>
       </c>
-      <c r="H2" t="s">
+      <c r="M2" t="s">
         <v>111</v>
       </c>
-      <c r="I2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" t="s">
-        <v>116</v>
-      </c>
       <c r="N2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O2">
         <v>46802</v>
@@ -2239,43 +2397,43 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E3" s="1">
         <v>28799</v>
       </c>
       <c r="F3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
         <v>100</v>
-      </c>
-      <c r="I3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M3" t="s">
-        <v>124</v>
-      </c>
-      <c r="N3" t="s">
-        <v>105</v>
       </c>
       <c r="O3">
         <v>47708</v>
@@ -2283,43 +2441,43 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E4" s="1">
         <v>29969</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M4" t="s">
+        <v>127</v>
+      </c>
+      <c r="N4" t="s">
         <v>100</v>
-      </c>
-      <c r="I4" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M4" t="s">
-        <v>132</v>
-      </c>
-      <c r="N4" t="s">
-        <v>105</v>
       </c>
       <c r="O4">
         <v>47401</v>
@@ -2327,46 +2485,46 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E5" s="1">
         <v>34859</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" t="s">
+        <v>134</v>
+      </c>
+      <c r="L5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N5" t="s">
         <v>100</v>
-      </c>
-      <c r="I5" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L5" t="s">
-        <v>140</v>
-      </c>
-      <c r="M5" t="s">
-        <v>141</v>
-      </c>
-      <c r="N5" t="s">
-        <v>105</v>
       </c>
       <c r="O5">
         <v>47901</v>
@@ -2374,40 +2532,40 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E6" s="1">
         <v>32398</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="M6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="N6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O6">
         <v>46402</v>
@@ -2415,43 +2573,43 @@
     </row>
     <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E7" s="1">
         <v>27511</v>
       </c>
       <c r="F7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" t="s">
+        <v>150</v>
+      </c>
+      <c r="M7" t="s">
+        <v>151</v>
+      </c>
+      <c r="N7" t="s">
         <v>100</v>
-      </c>
-      <c r="I7" t="s">
-        <v>101</v>
-      </c>
-      <c r="J7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" t="s">
-        <v>155</v>
-      </c>
-      <c r="M7" t="s">
-        <v>156</v>
-      </c>
-      <c r="N7" t="s">
-        <v>105</v>
       </c>
       <c r="O7">
         <v>47303</v>
@@ -2459,43 +2617,43 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E8" s="1">
         <v>33941</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" t="s">
+        <v>157</v>
+      </c>
+      <c r="L8" t="s">
+        <v>158</v>
+      </c>
+      <c r="M8" t="s">
+        <v>159</v>
+      </c>
+      <c r="N8" t="s">
         <v>100</v>
-      </c>
-      <c r="I8" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" t="s">
-        <v>162</v>
-      </c>
-      <c r="L8" t="s">
-        <v>163</v>
-      </c>
-      <c r="M8" t="s">
-        <v>164</v>
-      </c>
-      <c r="N8" t="s">
-        <v>105</v>
       </c>
       <c r="O8">
         <v>46032</v>
@@ -2503,43 +2661,43 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E9" s="1">
         <v>30913</v>
       </c>
       <c r="F9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>165</v>
+      </c>
+      <c r="M9" t="s">
+        <v>166</v>
+      </c>
+      <c r="N9" t="s">
         <v>100</v>
-      </c>
-      <c r="I9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" t="s">
-        <v>170</v>
-      </c>
-      <c r="M9" t="s">
-        <v>171</v>
-      </c>
-      <c r="N9" t="s">
-        <v>105</v>
       </c>
       <c r="O9">
         <v>47802</v>
@@ -2547,40 +2705,40 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E10" s="1">
         <v>35841</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>172</v>
+      </c>
+      <c r="M10" t="s">
+        <v>173</v>
+      </c>
+      <c r="N10" t="s">
         <v>100</v>
-      </c>
-      <c r="I10" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K10" t="s">
-        <v>177</v>
-      </c>
-      <c r="M10" t="s">
-        <v>178</v>
-      </c>
-      <c r="N10" t="s">
-        <v>105</v>
       </c>
       <c r="O10">
         <v>46601</v>
@@ -2588,46 +2746,46 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E11" s="1">
         <v>31557</v>
       </c>
       <c r="F11" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" t="s">
+        <v>180</v>
+      </c>
+      <c r="L11" t="s">
+        <v>181</v>
+      </c>
+      <c r="M11" t="s">
+        <v>182</v>
+      </c>
+      <c r="N11" t="s">
         <v>100</v>
-      </c>
-      <c r="I11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" t="s">
-        <v>185</v>
-      </c>
-      <c r="L11" t="s">
-        <v>186</v>
-      </c>
-      <c r="M11" t="s">
-        <v>187</v>
-      </c>
-      <c r="N11" t="s">
-        <v>105</v>
       </c>
       <c r="O11">
         <v>46514</v>
@@ -2635,46 +2793,46 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E12" s="1">
         <v>35199</v>
       </c>
       <c r="F12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" t="s">
+        <v>188</v>
+      </c>
+      <c r="L12" t="s">
+        <v>110</v>
+      </c>
+      <c r="M12" t="s">
+        <v>99</v>
+      </c>
+      <c r="N12" t="s">
         <v>100</v>
-      </c>
-      <c r="I12" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K12" t="s">
-        <v>193</v>
-      </c>
-      <c r="L12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M12" t="s">
-        <v>104</v>
-      </c>
-      <c r="N12" t="s">
-        <v>105</v>
       </c>
       <c r="O12">
         <v>46204</v>
@@ -2682,112 +2840,112 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" t="s">
         <v>201</v>
-      </c>
-      <c r="C20" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C22" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
